--- a/partner_results/pato/ClassMissingGermanDefinition_pato.xlsx
+++ b/partner_results/pato/ClassMissingGermanDefinition_pato.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,18 +446,18 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>pressure [pato]</t>
+          <t>physical object quality [pato]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>intensive quality</t>
+          <t>quality</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>A physical quality that inheres in a bearer by virtue of the bearer's amount of force per unit area it exerts.</t>
+          <t>A quality which inheres in a continuant.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -465,18 +465,18 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>length [pato]</t>
+          <t>quality of a solid [pato]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>morphology</t>
+          <t>quality of a substance [pato]</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>A 1-dimensional extent quality which is equal to the distance between two points.</t>
+          <t>A physical quality inhering in a bearer by virtue of the bearer's exhibiting the physical characteristics of an entity characterized by particles arranged such that their shape and volume are relatively stable.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -484,7 +484,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>acidity [pato]</t>
+          <t>viscosity [pato]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -495,7 +495,7 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>A concentration quality inhering in a bearer by virtue of the bearer's containing acid (hydrogen ions).</t>
+          <t>A physical quality of a fluid inhering in a bearer by virtue of the bearer's disposition to internal resistance to flow.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -503,7 +503,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>temperature [pato]</t>
+          <t>pressure [pato]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -514,7 +514,7 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>A physical quality of the thermal energy of a system.</t>
+          <t>A physical quality that inheres in a bearer by virtue of the bearer's amount of force per unit area it exerts.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -522,7 +522,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>physical object quality [pato]</t>
+          <t>quality of a substance [pato]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -533,7 +533,7 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>A quality which inheres in a continuant.</t>
+          <t>A quality inhering in a bearer by virtue of its constitution.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -541,18 +541,18 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>quality of a substance [pato]</t>
+          <t>temperature [pato]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>quality</t>
+          <t>intensive quality</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>A quality inhering in a bearer by virtue of its constitution.</t>
+          <t>A physical quality of the thermal energy of a system.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
@@ -560,18 +560,18 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>optical quality [pato]</t>
+          <t>acidity [pato]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>electromagnetic (EM) radiation quality</t>
+          <t>intensive quality</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>An EM radiation quality in which the EM radiation is within the fiat range of the spectrum visible deemed to be light.</t>
+          <t>A concentration quality inhering in a bearer by virtue of the bearer's containing acid (hydrogen ions).</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -579,18 +579,18 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>viscosity [pato]</t>
+          <t>length [pato]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>intensive quality</t>
+          <t>morphology</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>A physical quality of a fluid inhering in a bearer by virtue of the bearer's disposition to internal resistance to flow.</t>
+          <t>A 1-dimensional extent quality which is equal to the distance between two points.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -617,59 +617,21 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>quality of a solid [pato]</t>
+          <t>optical quality [pato]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>quality of a substance [pato]</t>
+          <t>electromagnetic (EM) radiation quality</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>A physical quality inhering in a bearer by virtue of the bearer's exhibiting the physical characteristics of an entity characterized by particles arranged such that their shape and volume are relatively stable.</t>
+          <t>An EM radiation quality in which the EM radiation is within the fiat range of the spectrum visible deemed to be light.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>shape [pato]</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>intensive quality</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>A morphological quality inhering in a bearer by virtue of the bearer's ratios of distances between its features (points, edges, surfaces and also holes etc).</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>shape [pato]</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>intensive quality</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>A morphological quality inhering in a bearer by virtue of the bearer's ratios of distances between its features (points, edges, surfaces and also holes etc).</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
